--- a/manuscript/_m/manuscript_supplement/supplementary_data/dataS02_composition_adjustment.xlsx
+++ b/manuscript/_m/manuscript_supplement/supplementary_data/dataS02_composition_adjustment.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>One row per analysis for the 12 analyses with an anatomically matched single-nucleus reference: genes tested, switch-unique genes before and after adding the estimated cell-type proportions to the conditional model, the number of unadjusted genes that remain (`n_overlap`) and the number that adjustment newly introduces (`n_new`), genes significant on both the switch and abundance coordinates in each arm, the number of cell types and samples covered by the deconvolution, and the number of module by cell-type marker tests with the counts reaching FDR &lt; 0.05 for depletion and for enrichment. Because adjustment both removes and adds genes, the adjusted set is not nested in the unadjusted one, so `n_overlap` divided by the unadjusted count – not the ratio of the two counts – is the persistence statistic. The five GTEx regions with no matched reference are absent by design rather than entered as zeros. Backs Fig. 2c,d and Fig. S14d.</t>
+          <t>One row per analysis for the 12 analyses with an anatomically matched single-nucleus reference: genes tested, switch-unique genes before and after adding the estimated cell-type proportions to the conditional model, the number of unadjusted genes that remain (`n_overlap`) and the number that adjustment newly introduces (`n_new`), genes significant on both the switch and abundance coordinates in each arm, the number of cell types and samples covered by the deconvolution, and the number of module-by-cell-type marker tests with the counts reaching false discovery rate (FDR) &lt; 0.05 for depletion and for enrichment. Because adjustment both removes and adds genes, the adjusted set is not nested in the unadjusted one, so `n_overlap` divided by the unadjusted count – not the ratio of the two counts – is the persistence statistic. The five Genotype-Tissue Expression (GTEx) regions with no matched reference are absent by design rather than entered as zeros. Backs Fig. 2c,d and Fig. S14d.</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 by manuscript/_h/build_supplementary_data.py</t>
+          <t>2026-10-04 by manuscript/_h/build_supplementary_data.py</t>
         </is>
       </c>
     </row>
